--- a/registry/exported_registry.xlsx
+++ b/registry/exported_registry.xlsx
@@ -10,7 +10,8 @@
     <sheet name="Domain" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Entity" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Property" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Relationship" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Logic" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Relationship" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>fqn</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -448,7 +449,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>parent_code</t>
+          <t>parent_fqn</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -470,25 +471,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>core</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>财务域</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
+          <t>核心域</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>财务结算与核销</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>manual</t>
@@ -503,29 +496,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>采购订单管理</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>PO Management</t>
-        </is>
-      </c>
+          <t>财务域</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>procurement</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>采购订单与合同管理</t>
-        </is>
-      </c>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>manual</t>
@@ -548,17 +533,13 @@
           <t>采购域</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Procurement</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>采购核心业务流程</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>manual</t>
@@ -573,29 +554,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>supply_base</t>
+          <t>supply_chain</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>供应商管理</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Supplier Management</t>
-        </is>
-      </c>
+          <t>供应链域</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>procurement</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>供应商全生命周期管理</t>
-        </is>
-      </c>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>manual</t>
@@ -671,39 +644,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>proc.public.contract</t>
+          <t>core.public.material</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>material</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>采购合同</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
+          <t>物料</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>["proc.public.contract"]</t>
+          <t>["core.public.material"]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>采购合同主表</t>
-        </is>
-      </c>
+          <t>["core"]</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>manual</t>
@@ -718,39 +683,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>proc.public.goods_receipt</t>
+          <t>core.public.supplier</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>supplier</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>收货单</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Goods Receipt</t>
-        </is>
-      </c>
+          <t>供应商</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>["proc.public.goods_receipt"]</t>
+          <t>["core.public.supplier"]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>入库收货单</t>
-        </is>
-      </c>
+          <t>["core"]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>manual</t>
@@ -765,12 +722,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>proc.public.invoice</t>
+          <t>fin.public.invoice</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>invoice</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -778,14 +735,10 @@
           <t>发票</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>["proc.public.invoice"]</t>
+          <t>["fin.public.invoice"]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -793,11 +746,7 @@
           <t>["finance"]</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>采购发票表</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>manual</t>
@@ -812,27 +761,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>proc.public.payment</t>
+          <t>fin.public.invoice_line</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>invoice_line</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>付款记录</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Payment</t>
-        </is>
-      </c>
+          <t>发票行</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>["proc.public.payment"]</t>
+          <t>["fin.public.invoice_line"]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -840,11 +785,7 @@
           <t>["finance"]</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>付款核销记录</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>manual</t>
@@ -864,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PurchaseOrderLine</t>
+          <t>po_line</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -872,11 +813,7 @@
           <t>采购订单行</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Purchase Order Line</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>["proc.public.po_line"]</t>
@@ -884,14 +821,10 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>采购订单行项目表</t>
-        </is>
-      </c>
+          <t>["procurement"]</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>manual</t>
@@ -911,7 +844,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PurchaseOrder</t>
+          <t>po_order</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -919,11 +852,7 @@
           <t>采购订单</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Purchase Order</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>["proc.public.po_order"]</t>
@@ -931,14 +860,10 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>采购订单头表</t>
-        </is>
-      </c>
+          <t>["procurement"]</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>manual</t>
@@ -953,39 +878,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>proc.public.supplier</t>
+          <t>proc.public.vendor_eval</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>vendor_eval</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>供应商主数据</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Supplier Master</t>
-        </is>
-      </c>
+          <t>供应商评估</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>["proc.public.supplier"]</t>
+          <t>["proc.public.po_order", "core.public.supplier"]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>["supply_base"]</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>供应商基本信息表</t>
-        </is>
-      </c>
+          <t>["procurement"]</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>manual</t>
@@ -1000,39 +917,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>proc.public.supplier_qual</t>
+          <t>scm.public.inventory</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SupplierQualification</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>供应商资质</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Supplier Qualification</t>
-        </is>
-      </c>
+          <t>库存</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>["proc.public.supplier_qual"]</t>
+          <t>["scm.public.inventory"]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>["supply_base"]</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>供应商资质文件表</t>
-        </is>
-      </c>
+          <t>["supply_chain"]</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>manual</t>
@@ -1055,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1081,35 +990,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>is_fk</t>
+          <t>ref_property_fqn</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ref_property_fqn</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>name_cn</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>name_cn</t>
+          <t>name_en</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>name_en</t>
+          <t>source</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -1118,17 +1022,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>proc.public.contract.contract_no</t>
+          <t>core.public.material.category</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>proc.public.contract</t>
+          <t>core.public.material</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>varchar(32)</t>
+          <t>STRING</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1136,29 +1040,20 @@
           <t>false</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>合同编号</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>合同编号</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>物料类别</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1167,47 +1062,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>proc.public.contract.end_date</t>
+          <t>core.public.material.material_id</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>proc.public.contract</t>
+          <t>core.public.material</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>到期日期</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>到期日期</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>物料ID</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1216,47 +1102,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>proc.public.contract.id</t>
+          <t>core.public.material.material_name</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>proc.public.contract</t>
+          <t>core.public.material</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>STRING</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
           <t>false</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>物料名称</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1265,17 +1142,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>proc.public.contract.start_date</t>
+          <t>core.public.supplier.credit_score</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>proc.public.contract</t>
+          <t>core.public.supplier</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1283,29 +1160,20 @@
           <t>false</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>生效日期</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>生效日期</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>信用评分</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1314,17 +1182,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>proc.public.contract.supplier_id</t>
+          <t>core.public.supplier.region</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>proc.public.contract</t>
+          <t>core.public.supplier</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>STRING</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1332,33 +1200,20 @@
           <t>false</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>proc.public.supplier.id</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>供应商ID</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>供应商ID</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1367,17 +1222,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>proc.public.contract.total_amt</t>
+          <t>core.public.supplier.risk_level</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>proc.public.contract</t>
+          <t>core.public.supplier</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>decimal(18,2)</t>
+          <t>STRING</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1385,29 +1240,20 @@
           <t>false</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>合同金额</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>合同金额</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>风险等级</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1416,17 +1262,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>proc.public.goods_receipt.id</t>
+          <t>core.public.supplier.supplier_id</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>proc.public.goods_receipt</t>
+          <t>core.public.supplier</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1434,29 +1280,20 @@
           <t>true</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>供应商ID</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1465,17 +1302,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>proc.public.goods_receipt.po_line_id</t>
+          <t>core.public.supplier.supplier_name</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>proc.public.goods_receipt</t>
+          <t>core.public.supplier</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>STRING</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1483,33 +1320,20 @@
           <t>false</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>proc.public.po_line.id</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>采购订单行ID</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>采购订单行ID</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>供应商名称</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1518,17 +1342,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>proc.public.goods_receipt.receipt_date</t>
+          <t>core.public.supplier.tax_id</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>proc.public.goods_receipt</t>
+          <t>core.public.supplier</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>STRING</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1536,29 +1360,20 @@
           <t>false</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>收货日期</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>收货日期</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>税号</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1567,17 +1382,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>proc.public.goods_receipt.receipt_qty</t>
+          <t>fin.public.invoice.invoice_date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>proc.public.goods_receipt</t>
+          <t>fin.public.invoice</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>decimal(18,4)</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1585,29 +1400,20 @@
           <t>false</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>实收数量</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>实收数量</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>发票日期</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1616,47 +1422,38 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>proc.public.invoice.amount</t>
+          <t>fin.public.invoice.invoice_id</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>proc.public.invoice</t>
+          <t>fin.public.invoice</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>decimal(18,2)</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>发票金额</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>发票金额</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>发票ID</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1665,47 +1462,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>proc.public.invoice.id</t>
+          <t>fin.public.invoice.po_order_id</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>proc.public.invoice</t>
+          <t>fin.public.invoice</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>proc.public.po_order.po_order_id</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>采购订单ID</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1714,17 +1506,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>proc.public.invoice.invoice_date</t>
+          <t>fin.public.invoice.tax_amount</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>proc.public.invoice</t>
+          <t>fin.public.invoice</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>DOUBLE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1732,29 +1524,20 @@
           <t>false</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>开票日期</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>开票日期</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>税额</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1763,17 +1546,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>proc.public.invoice.invoice_no</t>
+          <t>fin.public.invoice.total_amount</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>proc.public.invoice</t>
+          <t>fin.public.invoice</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>varchar(32)</t>
+          <t>DOUBLE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1781,29 +1564,20 @@
           <t>false</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>发票号码</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>发票号码</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>发票总额</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1812,17 +1586,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>proc.public.invoice.po_order_id</t>
+          <t>fin.public.invoice_line.amount</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>proc.public.invoice</t>
+          <t>fin.public.invoice_line</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>DOUBLE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1830,33 +1604,20 @@
           <t>false</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>proc.public.po_order.id</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>采购订单ID</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>采购订单ID</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>行金额</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1865,17 +1626,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>proc.public.invoice.tax_amt</t>
+          <t>fin.public.invoice_line.invoice_id</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>proc.public.invoice</t>
+          <t>fin.public.invoice_line</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>decimal(18,2)</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1885,27 +1646,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>fin.public.invoice.invoice_id</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>税额</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>税额</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>发票ID</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1914,17 +1670,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>proc.public.payment.id</t>
+          <t>fin.public.invoice_line.invoice_line_id</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>proc.public.payment</t>
+          <t>fin.public.invoice_line</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1932,29 +1688,20 @@
           <t>true</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>发票行ID</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1963,17 +1710,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>proc.public.payment.invoice_id</t>
+          <t>fin.public.invoice_line.po_line_id</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>proc.public.payment</t>
+          <t>fin.public.invoice_line</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1983,31 +1730,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>proc.public.invoice.id</t>
-        </is>
-      </c>
+          <t>proc.public.po_line.po_line_id</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>发票ID</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>发票ID</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>采购行ID</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2016,17 +1754,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>proc.public.payment.pay_amt</t>
+          <t>proc.public.po_line.line_amount</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>proc.public.payment</t>
+          <t>proc.public.po_line</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>decimal(18,2)</t>
+          <t>DOUBLE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2034,29 +1772,20 @@
           <t>false</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>付款金额</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>付款金额</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>行金额</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2065,17 +1794,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>proc.public.payment.pay_date</t>
+          <t>proc.public.po_line.material_id</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>proc.public.payment</t>
+          <t>proc.public.po_line</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2085,27 +1814,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>core.public.material.material_id</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>付款日期</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>付款日期</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>物料ID</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2114,7 +1838,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>proc.public.po_line.id</t>
+          <t>proc.public.po_line.po_line_id</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2124,7 +1848,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2132,29 +1856,20 @@
           <t>true</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>行ID</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2163,7 +1878,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>proc.public.po_line.line_amt</t>
+          <t>proc.public.po_line.po_order_id</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2173,7 +1888,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>decimal(18,2)</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2183,27 +1898,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>proc.public.po_order.po_order_id</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>行金额</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>行金额</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>订单ID</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2212,7 +1922,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>proc.public.po_line.line_no</t>
+          <t>proc.public.po_line.quantity</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2222,7 +1932,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2230,29 +1940,20 @@
           <t>false</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>行号</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>行号</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2261,7 +1962,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>proc.public.po_line.material_code</t>
+          <t>proc.public.po_line.unit_price</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2271,7 +1972,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>varchar(64)</t>
+          <t>DOUBLE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2279,29 +1980,20 @@
           <t>false</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>物料编码</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>物料编码</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>单价</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2310,17 +2002,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>proc.public.po_line.po_order_id</t>
+          <t>proc.public.po_order.order_date</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>proc.public.po_line</t>
+          <t>proc.public.po_order</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2328,33 +2020,20 @@
           <t>false</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>proc.public.po_order.id</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>所属采购订单ID</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>所属采购订单ID</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>订单日期</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2363,47 +2042,38 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>proc.public.po_line.quantity</t>
+          <t>proc.public.po_order.po_order_id</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>proc.public.po_line</t>
+          <t>proc.public.po_order</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>decimal(18,4)</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>采购数量</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>采购数量</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>订单ID</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2412,17 +2082,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>proc.public.po_line.unit_price</t>
+          <t>proc.public.po_order.status</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>proc.public.po_line</t>
+          <t>proc.public.po_order</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>decimal(18,4)</t>
+          <t>STRING</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2430,29 +2100,20 @@
           <t>false</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>单价</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>订单状态</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2461,7 +2122,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>proc.public.po_order.contract_id</t>
+          <t>proc.public.po_order.supplier_id</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2471,7 +2132,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2481,31 +2142,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>proc.public.contract.id</t>
-        </is>
-      </c>
+          <t>core.public.supplier.supplier_id</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>合同ID</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>合同ID</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>供应商ID</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2514,7 +2166,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>proc.public.po_order.created_at</t>
+          <t>proc.public.po_order.total_amount</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2524,7 +2176,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>DOUBLE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2532,29 +2184,20 @@
           <t>false</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>创建时间</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>创建时间</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>订单总额</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2563,47 +2206,38 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>proc.public.po_order.currency</t>
+          <t>scm.public.inventory.inventory_id</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>proc.public.po_order</t>
+          <t>scm.public.inventory</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>varchar(8)</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>币种</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>币种</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>库存ID</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2612,47 +2246,42 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>proc.public.po_order.id</t>
+          <t>scm.public.inventory.material_id</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>proc.public.po_order</t>
+          <t>scm.public.inventory</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>core.public.material.material_id</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>物料ID</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2661,17 +2290,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>proc.public.po_order.order_no</t>
+          <t>scm.public.inventory.quantity_on_hand</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>proc.public.po_order</t>
+          <t>scm.public.inventory</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>varchar(32)</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2679,29 +2308,20 @@
           <t>false</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>采购订单编号</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>采购订单编号</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>在手数量</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2710,17 +2330,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>proc.public.po_order.status</t>
+          <t>scm.public.inventory.reorder_point</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>proc.public.po_order</t>
+          <t>scm.public.inventory</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>varchar(16)</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2728,576 +2348,20 @@
           <t>false</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>订单状态</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>订单状态</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>再订购点</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>proc.public.po_order.supplier_id</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>proc.public.po_order</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>proc.public.supplier.id</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>供应商ID</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>供应商ID</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>proc.public.po_order.total_amt</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>proc.public.po_order</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>decimal(18,2)</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>订单总金额</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>订单总金额</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>proc.public.supplier.code</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>proc.public.supplier</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>varchar(32)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>供应商编码</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>供应商编码</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>proc.public.supplier.created_at</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>proc.public.supplier</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>创建时间</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>创建时间</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>proc.public.supplier.id</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>proc.public.supplier</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>proc.public.supplier.name</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>proc.public.supplier</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>varchar(200)</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>供应商名称</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>供应商名称</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>proc.public.supplier.status</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>proc.public.supplier</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>varchar(16)</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>供应商状态</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>供应商状态</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>proc.public.supplier_qual.expire_date</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>proc.public.supplier_qual</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>有效期至</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>有效期至</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>proc.public.supplier_qual.id</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>proc.public.supplier_qual</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>proc.public.supplier_qual.qual_type</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>proc.public.supplier_qual</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>varchar(64)</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>资质类型</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>资质类型</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>proc.public.supplier_qual.supplier_id</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>proc.public.supplier_qual</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>proc.public.supplier.id</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>供应商ID</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>供应商ID</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -3314,36 +2378,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>src_fqn</t>
+          <t>fqn</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>dst_fqn</t>
+          <t>logic_type</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>rel_type</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>is_directed</t>
+          <t>name_cn</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>name_en</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -3352,17 +2426,369 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>proc.public.po_order</t>
+          <t>fin.invoice_line_subtotal</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>proc.public.goods_receipt</t>
+          <t>formula</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FLOWS_TO</t>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>发票行小计</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>fin.tax_calc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>total_amount * 0.13</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>税额计算</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>proc.line_amount_calc</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>quantity * unit_price</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>行金额计算</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>proc.order_total_calc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SUM(line_amount)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>订单总额汇总</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>proc.supplier_risk_rule</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CASE WHEN credit_score&lt;60 OR tax_id IS NULL THEN 'HIGH' WHEN credit_score&lt;80 THEN 'MEDIUM' ELSE 'LOW' END</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>供应商风险规则</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>proc.supplier_risk_sub_credit</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CASE WHEN credit_score&lt;60 THEN 'HIGH' WHEN credit_score&lt;80 THEN 'MEDIUM' ELSE 'LOW' END</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>信用检查</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>proc.supplier_risk_sub_tax</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CASE WHEN tax_id IS NULL OR tax_id='' THEN 'HIGH' ELSE 'LOW' END</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>税务检查</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>proc.vendor_eval_score</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>vendor_eval_model_v1(inv_acc,delivery_rate,defect_rate)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>供应商评估</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>scm.reorder_calc</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CASE WHEN quantity_on_hand &lt; reorder_point THEN 'REORDER' ELSE 'OK' END</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>补货判断</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>src_fqn</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>dst_fqn</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>rel_type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>is_directed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>proc.line_amount_calc</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>HAS_LOGIC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3380,17 +2806,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>proc.public.goods_receipt</t>
+          <t>procurement</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>proc.public.invoice</t>
+          <t>proc.order_total_calc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FLOWS_TO</t>
+          <t>HAS_LOGIC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3408,17 +2834,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>proc.public.invoice</t>
+          <t>procurement</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>proc.public.payment</t>
+          <t>proc.supplier_risk_rule</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FLOWS_TO</t>
+          <t>HAS_LOGIC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3436,17 +2862,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>proc.public.supplier</t>
+          <t>procurement</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>proc.public.contract</t>
+          <t>proc.vendor_eval_score</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>OWNS</t>
+          <t>HAS_LOGIC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3464,17 +2890,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>proc.public.supplier</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>proc.public.supplier_qual</t>
+          <t>fin.tax_calc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OWNS</t>
+          <t>HAS_LOGIC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3492,17 +2918,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>proc.public.supplier</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>supply_base</t>
+          <t>fin.invoice_line_subtotal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_LOGIC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3520,17 +2946,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>proc.public.supplier_qual</t>
+          <t>supply_chain</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>supply_base</t>
+          <t>scm.reorder_calc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_LOGIC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3548,17 +2974,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>proc.public.po_order</t>
+          <t>proc.public.po_order.supplier_id</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>core.public.supplier.supplier_id</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>FIELD_LINK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3576,17 +3002,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>proc.public.po_line</t>
+          <t>proc.public.po_line.po_order_id</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.po_order.po_order_id</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>FIELD_LINK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3604,17 +3030,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>proc.public.contract</t>
+          <t>proc.public.po_line.material_id</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>core.public.material.material_id</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>FIELD_LINK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3632,17 +3058,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>proc.public.goods_receipt</t>
+          <t>fin.public.invoice.po_order_id</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.po_order.po_order_id</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>FIELD_LINK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3660,17 +3086,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>proc.public.invoice</t>
+          <t>fin.public.invoice_line.invoice_id</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>fin.public.invoice.invoice_id</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>FIELD_LINK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3688,17 +3114,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>proc.public.payment</t>
+          <t>fin.public.invoice_line.po_line_id</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>proc.public.po_line.po_line_id</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>FIELD_LINK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3716,17 +3142,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>proc.public.supplier_qual.supplier_id</t>
+          <t>scm.public.inventory.material_id</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>proc.public.supplier.id</t>
+          <t>core.public.material.material_id</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>REFERENCES</t>
+          <t>FIELD_LINK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3744,17 +3170,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>proc.public.po_order.supplier_id</t>
+          <t>core.public.supplier</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>proc.public.supplier.id</t>
+          <t>proc.supplier_risk_rule</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>REFERENCES</t>
+          <t>USE_LOGIC</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3772,17 +3198,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>proc.public.po_order.contract_id</t>
+          <t>proc.public.po_order</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>proc.public.contract.id</t>
+          <t>proc.order_total_calc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>REFERENCES</t>
+          <t>USE_LOGIC</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3800,17 +3226,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>proc.public.po_line.po_order_id</t>
+          <t>proc.public.po_line</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>proc.public.po_order.id</t>
+          <t>proc.line_amount_calc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>REFERENCES</t>
+          <t>USE_LOGIC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3828,17 +3254,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>proc.public.contract.supplier_id</t>
+          <t>fin.public.invoice</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>proc.public.supplier.id</t>
+          <t>fin.tax_calc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>REFERENCES</t>
+          <t>USE_LOGIC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3856,17 +3282,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>proc.public.goods_receipt.po_line_id</t>
+          <t>fin.public.invoice_line</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>proc.public.po_line.id</t>
+          <t>fin.invoice_line_subtotal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>REFERENCES</t>
+          <t>USE_LOGIC</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3884,17 +3310,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>proc.public.invoice.po_order_id</t>
+          <t>scm.public.inventory</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>proc.public.po_order.id</t>
+          <t>scm.reorder_calc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>REFERENCES</t>
+          <t>USE_LOGIC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3912,17 +3338,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>proc.public.payment.invoice_id</t>
+          <t>proc.public.vendor_eval</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>proc.public.invoice.id</t>
+          <t>proc.vendor_eval_score</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>REFERENCES</t>
+          <t>USE_LOGIC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3940,17 +3366,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>proc.public.invoice</t>
+          <t>core.public.supplier</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>proc.public.po_order</t>
+          <t>core.public.supplier.supplier_id</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MATCHES</t>
+          <t>HAS_PROPERTY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3960,6 +3386,1378 @@
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>core.public.supplier</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>core.public.supplier.supplier_name</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>core.public.supplier</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>core.public.supplier.tax_id</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>core.public.supplier</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>core.public.supplier.credit_score</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>core.public.supplier</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>core.public.supplier.risk_level</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>core.public.supplier</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>core.public.supplier.region</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>core.public.material</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>core.public.material.material_id</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>core.public.material</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>core.public.material.material_name</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>core.public.material</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>core.public.material.category</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>proc.public.po_order</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>proc.public.po_order.po_order_id</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>proc.public.po_order</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>proc.public.po_order.supplier_id</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>proc.public.po_order</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>proc.public.po_order.order_date</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>proc.public.po_order</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>proc.public.po_order.status</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>proc.public.po_order</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>proc.public.po_order.total_amount</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>proc.public.po_line</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>proc.public.po_line.po_line_id</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>proc.public.po_line</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>proc.public.po_line.po_order_id</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>proc.public.po_line</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>proc.public.po_line.material_id</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>proc.public.po_line</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>proc.public.po_line.quantity</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>proc.public.po_line</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>proc.public.po_line.unit_price</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>proc.public.po_line</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>proc.public.po_line.line_amount</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>fin.public.invoice</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>fin.public.invoice.invoice_id</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>fin.public.invoice</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>fin.public.invoice.po_order_id</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>fin.public.invoice</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>fin.public.invoice.invoice_date</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>fin.public.invoice</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>fin.public.invoice.total_amount</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>fin.public.invoice</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>fin.public.invoice.tax_amount</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>fin.public.invoice_line</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>fin.public.invoice_line.invoice_line_id</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>fin.public.invoice_line</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>fin.public.invoice_line.invoice_id</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>fin.public.invoice_line</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>fin.public.invoice_line.po_line_id</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>fin.public.invoice_line</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>fin.public.invoice_line.amount</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>scm.public.inventory</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>scm.public.inventory.inventory_id</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>scm.public.inventory</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>scm.public.inventory.material_id</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>scm.public.inventory</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>scm.public.inventory.quantity_on_hand</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>scm.public.inventory</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>scm.public.inventory.reorder_point</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>HAS_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>proc.supplier_risk_rule</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>proc.supplier_risk_sub_tax</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DECOMPOSES_TO</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>proc.supplier_risk_rule</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>proc.supplier_risk_sub_credit</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>DECOMPOSES_TO</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>core.public.supplier</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>IN_DOMAIN</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>core.public.material</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>IN_DOMAIN</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>proc.public.po_order</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>IN_DOMAIN</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>proc.public.po_line</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>IN_DOMAIN</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>fin.public.invoice</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>IN_DOMAIN</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>fin.public.invoice_line</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>IN_DOMAIN</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>scm.public.inventory</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>IN_DOMAIN</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>proc.public.vendor_eval</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>IN_DOMAIN</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>DOMAIN_LINK</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>DOMAIN_LINK</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>DOMAIN_LINK</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>proc.line_amount_calc</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>proc.public.po_line.line_amount</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>COMPUTES</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>proc.order_total_calc</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>proc.public.po_order.total_amount</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>COMPUTES</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>proc.supplier_risk_rule</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>core.public.supplier.risk_level</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>COMPUTES</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>fin.tax_calc</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>fin.public.invoice.tax_amount</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>COMPUTES</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
         <is>
           <t>active</t>
         </is>
